--- a/out/Petra Speech Logs 2024-11 Nov to 2025-04 April - Nov 2x Petra absent, 2x clinician gone, 2x school closed, 2x sessions only.xlsx
+++ b/out/Petra Speech Logs 2024-11 Nov to 2025-04 April - Nov 2x Petra absent, 2x clinician gone, 2x school closed, 2x sessions only.xlsx
@@ -476,9 +476,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
@@ -496,17 +496,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Week of (Monday)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date of Service</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Day of Week</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Week of (Monday)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -553,17 +553,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>11/04/2024</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2024</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>11/04/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -578,18 +578,18 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>11/11/2024</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>11/12/2024</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>11/11/2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>11/12/2024</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>11/11/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>11/18/2024</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>11/19/2024</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11/18/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -745,18 +745,18 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -773,17 +773,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>11/25/2024</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>11/26/2024</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11/25/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -798,18 +798,18 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>12/02/2024</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
           <t>12/03/2024</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>12/02/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>10:30 -11:00 Supported during morning meeting and group project (tree decorating) put on ___ where are you? responded on AAC with prompting answering WH ?'s re: day, month, weather, daily activity. -- responded 2x/ independently, 2x with prompting 11:00-11:30 Pete the Cat Snow Daze WH ?'s winter clothing yes/no</t>
+          <t>Supported during morning meeting and group project (tree decorating) put on ___ where are you? responded on AAC with prompting answering WH ?'s re: day, month, weather, daily activity. -- responded 2x/ independently, 2x with prompting 11:00-11:30 Pete the Cat Snow Daze WH ?'s winter clothing yes/no</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>12/09/2024</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
           <t>12/10/2024</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>12/09/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>9:30-10:00 - facilitated communication during morning meeting and morning leisure activities responding yes/no to questions using comm board following directions with movements along with song 10-10:30 Winter vocab + picture finds I see ___ - 3 word utterance 3x identifying pic based on label 100% identifying pic based on attribute w/ model only During play time, Petra grabbed SLP's hand without saying anything. Given prompting "hold my hand please" and "play with me" she repeated "play with me please"</t>
+          <t>- facilitated communication during morning meeting and morning leisure activities responding yes/no to questions using comm board following directions with movements along with song 10-10:30 Winter vocab + picture finds I see ___ - 3 word utterance 3x identifying pic based on label 100% identifying pic based on attribute w/ model only During play time, Petra grabbed SLP's hand without saying anything. Given prompting "hold my hand please" and "play with me" she repeated "play with me please"</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -940,17 +940,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>12/16/2024</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>12/17/2024</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>12/16/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>9:30-10: facilitated morning meeting and worked on answering questions, responding when called on, following directions, and labeling on AAC w/ model 10-10:30: co treat with OT -- making puffy paint + painting polar bear, video requesting color, more, continued action on AAC w/ model and voice yes/no on AAC w/ model and voice labeling from video using visual cues on AAC w/ model</t>
+          <t>-10: facilitated morning meeting and worked on answering questions, responding when called on, following directions, and labeling on AAC w/ model 10-10:30: co treat with OT -- making puffy paint + painting polar bear, video requesting color, more, continued action on AAC w/ model and voice yes/no on AAC w/ model and voice labeling from video using visual cues on AAC w/ model</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>12/23/2024</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>12/24/2024</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12/23/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>12/30/2024</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>12/31/2024</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12/30/2024</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>01/06/2025</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>01/07/2025</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>01/13/2025</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
           <t>01/14/2025</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>01/13/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>9:30-10 Free play time w/ playdoh. Worked on following directions w/ movements (i.e. roll, smash, etc). Petra was observed to repeat these words after hearing models. Later in the morning, Petra expressed requests during snack time. 10-10:30 Yeti book prompted to get device from table. Needed multiple prompts to remain focused on the task. she plugged her ears when SLP started reading aloud and walked away. Brought cheerios back to the table. She did not respond to questions during reading. Given models to express "I do" or "I don't" when asked if she liked various things when she appeared to attempt independently she said "dad mom"</t>
+          <t>-10 Free play time w/ playdoh. Worked on following directions w/ movements (i.e. roll, smash, etc). Petra was observed to repeat these words after hearing models. Later in the morning, Petra expressed requests during snack time. 10-10:30 Yeti book prompted to get device from table. Needed multiple prompts to remain focused on the task. she plugged her ears when SLP started reading aloud and walked away. Brought cheerios back to the table. She did not respond to questions during reading. Given models to express "I do" or "I don't" when asked if she liked various things when she appeared to attempt independently she said "dad mom"</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1225,17 +1225,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>01/20/2025</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
           <t>01/21/2025</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1282,17 +1282,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>01/27/2025</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
           <t>01/28/2025</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>02/03/2025</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
           <t>02/04/2025</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>9:30-10 -- morning meeting -- with visuals and verbal prompting, and AAC w/ verb prompts, engaged by responding to WH questions re: calendar, weather, who is at school today? 3/3 1:00-1:30 -- target words stop/go, touched visuals and verbalized single words, 2 words w/ model on AAC, performed actions for driving and pushing 3/10, model to label items - touched when heard label 6/10 left area 3 times, redirected with tactile prompt to return to seat. Throughout the day, observations: walked up a handed empty cup to SLP -- with starter "I want..." Petra vocalized "I want more water" walked up and appeared to want a hug -- with starter "Can I have..." Petra vocalized "hug"</t>
+          <t>-10 -- morning meeting -- with visuals and verbal prompting, and AAC w/ verb prompts, engaged by responding to WH questions re: calendar, weather, who is at school today? 3/3 1:00-1:30 -- target words stop/go, touched visuals and verbalized single words, 2 words w/ model on AAC, performed actions for driving and pushing 3/10, model to label items - touched when heard label 6/10 left area 3 times, redirected with tactile prompt to return to seat. Throughout the day, observations: walked up a handed empty cup to SLP -- with starter "I want..." Petra vocalized "I want more water" walked up and appeared to want a hug -- with starter "Can I have..." Petra vocalized "hug"</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>02/10/2025</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>02/11/2025</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1421,18 +1421,18 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>02/17/2025</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
           <t>02/18/2025</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>02/17/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025. SELF REGULATION: Given modeling, a fading prompt hierarchy, reinforcement, a visual list of strategies, multimodal communication and opportunities for practice, Petra will demonstrate an understanding of emotions, engage in calming strategies and adapt to changes in her routine in 4 out of 5 trials with 80% accuracy by May 9, 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025. SELF REGULATION: Given modeling, a fading prompt hierarchy, reinforcement, a visual list of strategies, multimodal communication and opportunities for practice, Petra will demonstrate an understanding of emotions, engage in calming strategies and adapt to changes in her routine in 4 out of 5 trials with 80% accuracy by May 9, 2025.</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>9:30-10 morning meeting, facilitating communication in the classroom - WH questions, commenting, social greetings and responses. 10-10:30 Little Blue Truck Valentines labeling animals 4/7 independently Identifying objects by color w/ choice of 2 -- 40% acc -- lack of attention to task observed "give to ____ (animal)" direction -- 5/8 independently</t>
+          <t>-10 morning meeting, facilitating communication in the classroom - WH questions, commenting, social greetings and responses. 10-10:30 Little Blue Truck Valentines labeling animals 4/7 independently Identifying objects by color w/ choice of 2 -- 40% acc -- lack of attention to task observed "give to ____ (animal)" direction -- 5/8 independently</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>02/24/2025</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>02/25/2025</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>02/24/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1531,18 +1531,18 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1559,17 +1559,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
           <t>03/04/2025</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
           <t>03/11/2025</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>03/17/2025</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
           <t>03/18/2025</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>03/17/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>03/24/2025</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
           <t>03/25/2025</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>03/24/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>03/31/2025</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
           <t>04/01/2025</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
           <t>04/08/2025</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>04/15/2025</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>(BLANK)</t>
+          <t>(LEFT BLANK)</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1958,17 +1958,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>04/21/2025</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
           <t>04/22/2025</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>04/21/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>04/28/2025</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
           <t>04/29/2025</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>04/28/2025</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>1:1 activity -- needed tactile prompting to remain in area. Without tactile prompts, she eloped the designated area frequently and when redirected to come back, she would get upset. Story: I found the ___ 5x w/ sentence frame and model he eat open the egg no response to yes/no questions "do you like ___?" What did he do? phonemic cue for response Supported during morning meeting -- able to participate verbally when she was in her designated area and attending. Needed frequent prompting for attention.</t>
+          <t>activity -- needed tactile prompting to remain in area. Without tactile prompts, she eloped the designated area frequently and when redirected to come back, she would get upset. Story: I found the ___ 5x w/ sentence frame and model he eat open the egg no response to yes/no questions "do you like ___?" What did he do? phonemic cue for response Supported during morning meeting -- able to participate verbally when she was in her designated area and attending. Needed frequent prompting for attention.</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">

--- a/out/Petra Speech Logs 2024-11 Nov to 2025-04 April - Nov 2x Petra absent, 2x clinician gone, 2x school closed, 2x sessions only.xlsx
+++ b/out/Petra Speech Logs 2024-11 Nov to 2025-04 April - Nov 2x Petra absent, 2x clinician gone, 2x school closed, 2x sessions only.xlsx
@@ -581,7 +581,11 @@
           <t>(LEFT BLANK)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -748,7 +752,11 @@
           <t>(LEFT BLANK)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -801,7 +809,11 @@
           <t>(LEFT BLANK)</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -1424,7 +1436,11 @@
           <t>(LEFT BLANK)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
@@ -1534,7 +1550,11 @@
           <t>(LEFT BLANK)</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>(LEFT BLANK)</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
           <t>(LEFT BLANK)</t>
